--- a/Result/profitability/6282.xlsx
+++ b/Result/profitability/6282.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05875</v>
+        <v>0.1025</v>
       </c>
       <c r="N2" t="n">
-        <v>23.2675</v>
+        <v>23.07</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0.16375</v>
+        <v>0.155</v>
       </c>
       <c r="N3" t="n">
-        <v>22.4025</v>
+        <v>22.235</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0.225</v>
+        <v>0.2425</v>
       </c>
       <c r="N4" t="n">
-        <v>21.8325</v>
+        <v>21.28875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>0.295</v>
+        <v>0.385</v>
       </c>
       <c r="N5" t="n">
-        <v>21.09125</v>
+        <v>20.5675</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>0.435</v>
+        <v>0.40875</v>
       </c>
       <c r="N6" t="n">
-        <v>20.2125</v>
+        <v>19.715</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>0.45375</v>
+        <v>0.395</v>
       </c>
       <c r="N7" t="n">
-        <v>19.3375</v>
+        <v>18.67</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.59</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4575</v>
+        <v>0.435</v>
       </c>
       <c r="N8" t="n">
-        <v>18.17875</v>
+        <v>17.785</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.57</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4949999999999999</v>
+        <v>0.495</v>
       </c>
       <c r="N9" t="n">
         <v>17.21</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6282</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9515</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7494</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>140</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>129</v>
+      </c>
+      <c r="K75" t="n">
+        <v>78</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.05500000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.23125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.150000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1291512915129153</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.190000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1647660243806528</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
